--- a/mode_docx_gen/pmi_lodzt/lot_modes/ЛО Т_11.xlsx
+++ b/mode_docx_gen/pmi_lodzt/lot_modes/ЛО Т_11.xlsx
@@ -764,8 +764,8 @@
       <c r="AG2" t="n">
         <v>0</v>
       </c>
-      <c r="AH2" t="n">
-        <v>0</v>
+      <c r="AH2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1113,11 +1113,11 @@
       <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1695,9 +1695,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1735,9 +1735,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AU2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
